--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/74.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/74.xlsx
@@ -426,13 +426,13 @@
         <v>-11.94538740614331</v>
       </c>
       <c r="E2">
-        <v>-11.05002207230419</v>
+        <v>-11.27313998666211</v>
       </c>
       <c r="F2">
-        <v>-3.177214917828651</v>
+        <v>-3.274346794378713</v>
       </c>
       <c r="G2">
-        <v>-12.65465748035309</v>
+        <v>-10.18011407447743</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.39970911302585</v>
       </c>
       <c r="E3">
-        <v>-11.54780552064934</v>
+        <v>-11.74276538362757</v>
       </c>
       <c r="F3">
-        <v>-3.218976232073385</v>
+        <v>-3.267601398617716</v>
       </c>
       <c r="G3">
-        <v>-11.85451848678447</v>
+        <v>-9.634314363054411</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-10.85160897964161</v>
       </c>
       <c r="E4">
-        <v>-11.52031315494878</v>
+        <v>-12.82943612040418</v>
       </c>
       <c r="F4">
-        <v>-3.016157928804551</v>
+        <v>-3.195214513124081</v>
       </c>
       <c r="G4">
-        <v>-12.41828121830358</v>
+        <v>-10.59459768653972</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.37130779780972</v>
       </c>
       <c r="E5">
-        <v>-12.43730649913199</v>
+        <v>-13.38066914746186</v>
       </c>
       <c r="F5">
-        <v>-3.107004981869573</v>
+        <v>-3.403599445339728</v>
       </c>
       <c r="G5">
-        <v>-11.98043508637065</v>
+        <v>-9.993247020967733</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-9.94044827129097</v>
       </c>
       <c r="E6">
-        <v>-12.96865499682199</v>
+        <v>-14.71654180888057</v>
       </c>
       <c r="F6">
-        <v>-3.176013785094591</v>
+        <v>-3.518478265127366</v>
       </c>
       <c r="G6">
-        <v>-11.50707011134689</v>
+        <v>-9.817910597571313</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-9.556232970474259</v>
       </c>
       <c r="E7">
-        <v>-13.92077571388269</v>
+        <v>-15.45294413811189</v>
       </c>
       <c r="F7">
-        <v>-3.163000133196611</v>
+        <v>-3.459770210556159</v>
       </c>
       <c r="G7">
-        <v>-11.5070800429835</v>
+        <v>-9.934445111099198</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-9.20025309807985</v>
       </c>
       <c r="E8">
-        <v>-14.74647502207127</v>
+        <v>-15.7246435216241</v>
       </c>
       <c r="F8">
-        <v>-3.2622112119277</v>
+        <v>-3.247880455859268</v>
       </c>
       <c r="G8">
-        <v>-10.82110521233666</v>
+        <v>-9.897145194508228</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-8.864750988093956</v>
       </c>
       <c r="E9">
-        <v>-15.65251398762992</v>
+        <v>-16.52601586744347</v>
       </c>
       <c r="F9">
-        <v>-3.17535357627456</v>
+        <v>-3.088620195731841</v>
       </c>
       <c r="G9">
-        <v>-11.33300162689201</v>
+        <v>-8.940672308938614</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-8.531436189471105</v>
       </c>
       <c r="E10">
-        <v>-16.56631022916372</v>
+        <v>-17.77612375963091</v>
       </c>
       <c r="F10">
-        <v>-3.010600411899169</v>
+        <v>-3.204151769032885</v>
       </c>
       <c r="G10">
-        <v>-11.24629181812742</v>
+        <v>-9.54787601902404</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-8.191836422510827</v>
       </c>
       <c r="E11">
-        <v>-16.74020363105826</v>
+        <v>-18.23690957533339</v>
       </c>
       <c r="F11">
-        <v>-3.228660675379514</v>
+        <v>-3.527548059820618</v>
       </c>
       <c r="G11">
-        <v>-10.37391009980083</v>
+        <v>-8.91653181086625</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-7.836787101955672</v>
       </c>
       <c r="E12">
-        <v>-17.78052090789236</v>
+        <v>-18.83800562968953</v>
       </c>
       <c r="F12">
-        <v>-2.892617699453242</v>
+        <v>-3.304472860083725</v>
       </c>
       <c r="G12">
-        <v>-10.22384307050567</v>
+        <v>-7.969702544452533</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.458826620813864</v>
       </c>
       <c r="E13">
-        <v>-18.55934598162753</v>
+        <v>-19.69302227860376</v>
       </c>
       <c r="F13">
-        <v>-2.895542664752527</v>
+        <v>-3.276527057382881</v>
       </c>
       <c r="G13">
-        <v>-9.017708703637455</v>
+        <v>-7.582871919279773</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.065596534383887</v>
       </c>
       <c r="E14">
-        <v>-19.14488219929332</v>
+        <v>-20.75840013059631</v>
       </c>
       <c r="F14">
-        <v>-2.841711209081601</v>
+        <v>-2.943290590217293</v>
       </c>
       <c r="G14">
-        <v>-9.358555851269738</v>
+        <v>-7.000209283276966</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.666270367881829</v>
       </c>
       <c r="E15">
-        <v>-19.48250257893518</v>
+        <v>-21.88535617214515</v>
       </c>
       <c r="F15">
-        <v>-2.857530541372863</v>
+        <v>-3.012513112232234</v>
       </c>
       <c r="G15">
-        <v>-8.670005416193343</v>
+        <v>-6.401877835236788</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.276639070098612</v>
       </c>
       <c r="E16">
-        <v>-20.17774560791079</v>
+        <v>-21.5344628351868</v>
       </c>
       <c r="F16">
-        <v>-2.822748222496714</v>
+        <v>-2.903056785463321</v>
       </c>
       <c r="G16">
-        <v>-8.43980994266566</v>
+        <v>-5.864854380038373</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.920167974868897</v>
       </c>
       <c r="E17">
-        <v>-22.08562340666036</v>
+        <v>-22.38385964785752</v>
       </c>
       <c r="F17">
-        <v>-2.468067808374856</v>
+        <v>-2.994906991453133</v>
       </c>
       <c r="G17">
-        <v>-7.129459602221192</v>
+        <v>-5.736789236397207</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.615837733951393</v>
       </c>
       <c r="E18">
-        <v>-21.88725813122837</v>
+        <v>-23.8794153597347</v>
       </c>
       <c r="F18">
-        <v>-2.155919918549738</v>
+        <v>-2.643456381834789</v>
       </c>
       <c r="G18">
-        <v>-7.579220387549957</v>
+        <v>-5.143774524493097</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.379573573632198</v>
       </c>
       <c r="E19">
-        <v>-23.35854122242444</v>
+        <v>-24.43582896105716</v>
       </c>
       <c r="F19">
-        <v>-1.907714536914116</v>
+        <v>-2.289944794118281</v>
       </c>
       <c r="G19">
-        <v>-7.069131530859052</v>
+        <v>-4.952769289059307</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.2178813607481</v>
       </c>
       <c r="E20">
-        <v>-23.58504190686609</v>
+        <v>-25.38646886711736</v>
       </c>
       <c r="F20">
-        <v>-1.9857972766694</v>
+        <v>-2.194246821542465</v>
       </c>
       <c r="G20">
-        <v>-6.807194546700837</v>
+        <v>-4.519038165231693</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.120911306310132</v>
       </c>
       <c r="E21">
-        <v>-24.32925585376064</v>
+        <v>-25.54629682874408</v>
       </c>
       <c r="F21">
-        <v>-1.883622299371095</v>
+        <v>-1.897008716600335</v>
       </c>
       <c r="G21">
-        <v>-7.089610565564985</v>
+        <v>-4.154404747899746</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.071616111665653</v>
       </c>
       <c r="E22">
-        <v>-24.82449882818749</v>
+        <v>-26.79402274360348</v>
       </c>
       <c r="F22">
-        <v>-1.320679551409204</v>
+        <v>-1.749700141360499</v>
       </c>
       <c r="G22">
-        <v>-7.230252471709842</v>
+        <v>-3.822317303764375</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-5.043258920956996</v>
       </c>
       <c r="E23">
-        <v>-25.84755809057835</v>
+        <v>-27.40956463004409</v>
       </c>
       <c r="F23">
-        <v>-1.346474083964978</v>
+        <v>-1.531856910139688</v>
       </c>
       <c r="G23">
-        <v>-6.748664101566523</v>
+        <v>-4.159062685473501</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.005510616534769</v>
       </c>
       <c r="E24">
-        <v>-25.87201185021977</v>
+        <v>-27.95773640867259</v>
       </c>
       <c r="F24">
-        <v>-1.15153438306417</v>
+        <v>-1.31548817289586</v>
       </c>
       <c r="G24">
-        <v>-7.07336902914932</v>
+        <v>-3.855796850803025</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.936467333156891</v>
       </c>
       <c r="E25">
-        <v>-26.43391849051353</v>
+        <v>-28.742013765113</v>
       </c>
       <c r="F25">
-        <v>-1.047693558918836</v>
+        <v>-1.125473116204695</v>
       </c>
       <c r="G25">
-        <v>-7.574625350341448</v>
+        <v>-3.651066093563416</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.818190887482283</v>
       </c>
       <c r="E26">
-        <v>-26.31820692266954</v>
+        <v>-28.15637792101905</v>
       </c>
       <c r="F26">
-        <v>-1.201410384386729</v>
+        <v>-1.426248349956779</v>
       </c>
       <c r="G26">
-        <v>-7.254359864326815</v>
+        <v>-4.213934977786921</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.64391297343743</v>
       </c>
       <c r="E27">
-        <v>-26.16180248739262</v>
+        <v>-28.2228876187697</v>
       </c>
       <c r="F27">
-        <v>-1.125985047259625</v>
+        <v>-1.283493310330132</v>
       </c>
       <c r="G27">
-        <v>-7.440349623268609</v>
+        <v>-4.650566139506937</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.420422766601348</v>
       </c>
       <c r="E28">
-        <v>-26.22694005751895</v>
+        <v>-28.19676738069346</v>
       </c>
       <c r="F28">
-        <v>-1.013599613354414</v>
+        <v>-1.203870635573043</v>
       </c>
       <c r="G28">
-        <v>-6.813878538144627</v>
+        <v>-4.909957314145452</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.161692596889673</v>
       </c>
       <c r="E29">
-        <v>-26.40701029795996</v>
+        <v>-28.06482576200597</v>
       </c>
       <c r="F29">
-        <v>-0.9211571246715999</v>
+        <v>-1.203441541258393</v>
       </c>
       <c r="G29">
-        <v>-7.618718506379001</v>
+        <v>-4.441902454166674</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.890361333917977</v>
       </c>
       <c r="E30">
-        <v>-26.11385500459941</v>
+        <v>-28.4514849866769</v>
       </c>
       <c r="F30">
-        <v>-1.011789630579297</v>
+        <v>-1.384835778388623</v>
       </c>
       <c r="G30">
-        <v>-7.768073768383221</v>
+        <v>-4.809571641758132</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.630705748640302</v>
       </c>
       <c r="E31">
-        <v>-26.89373521277837</v>
+        <v>-28.32928864405392</v>
       </c>
       <c r="F31">
-        <v>-1.33884647692</v>
+        <v>-1.180222402957923</v>
       </c>
       <c r="G31">
-        <v>-7.816420975438738</v>
+        <v>-5.602053343494409</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.403690576571935</v>
       </c>
       <c r="E32">
-        <v>-25.9184921074345</v>
+        <v>-28.0429351186529</v>
       </c>
       <c r="F32">
-        <v>-1.247007039706425</v>
+        <v>-1.301333859084225</v>
       </c>
       <c r="G32">
-        <v>-7.380230116275444</v>
+        <v>-4.492418068550413</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.227863577095104</v>
       </c>
       <c r="E33">
-        <v>-25.99763171919255</v>
+        <v>-27.70315465690937</v>
       </c>
       <c r="F33">
-        <v>-1.09921055606634</v>
+        <v>-1.50559352163393</v>
       </c>
       <c r="G33">
-        <v>-7.528257849518416</v>
+        <v>-4.79382006608228</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.11285955398937</v>
       </c>
       <c r="E34">
-        <v>-24.94881902512006</v>
+        <v>-28.04714659948003</v>
       </c>
       <c r="F34">
-        <v>-0.9213882391769811</v>
+        <v>-1.524092622473248</v>
       </c>
       <c r="G34">
-        <v>-7.026819448321628</v>
+        <v>-4.468790705036635</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.062957139818343</v>
       </c>
       <c r="E35">
-        <v>-25.58786822013449</v>
+        <v>-26.52738619403185</v>
       </c>
       <c r="F35">
-        <v>-0.8941374367270857</v>
+        <v>-1.377813707915092</v>
       </c>
       <c r="G35">
-        <v>-7.822207809041384</v>
+        <v>-3.873024929789392</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.077033658100749</v>
       </c>
       <c r="E36">
-        <v>-24.43177144834629</v>
+        <v>-27.21321452554551</v>
       </c>
       <c r="F36">
-        <v>-1.241327752792831</v>
+        <v>-1.613024490102998</v>
       </c>
       <c r="G36">
-        <v>-6.783593667551374</v>
+        <v>-4.511423910491369</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.14546613322393</v>
       </c>
       <c r="E37">
-        <v>-24.69198662177504</v>
+        <v>-26.06258362188456</v>
       </c>
       <c r="F37">
-        <v>-1.254921261872771</v>
+        <v>-1.538439945889736</v>
       </c>
       <c r="G37">
-        <v>-5.82257871350188</v>
+        <v>-4.644087401886583</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.255022275656797</v>
       </c>
       <c r="E38">
-        <v>-25.15188032809801</v>
+        <v>-26.00724114103683</v>
       </c>
       <c r="F38">
-        <v>-1.570518473563146</v>
+        <v>-1.775362963499228</v>
       </c>
       <c r="G38">
-        <v>-6.236098956812244</v>
+        <v>-4.337477916221443</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.390154511275643</v>
       </c>
       <c r="E39">
-        <v>-24.83187571234598</v>
+        <v>-25.25879759941911</v>
       </c>
       <c r="F39">
-        <v>-1.550189509131044</v>
+        <v>-2.049322287687886</v>
       </c>
       <c r="G39">
-        <v>-6.073160526460395</v>
+        <v>-4.146969262618543</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.535114946228215</v>
       </c>
       <c r="E40">
-        <v>-23.91091995340607</v>
+        <v>-26.0130692870847</v>
       </c>
       <c r="F40">
-        <v>-1.466184770813146</v>
+        <v>-1.894483852756602</v>
       </c>
       <c r="G40">
-        <v>-5.717283502079821</v>
+        <v>-3.915469434148388</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.677763174122916</v>
       </c>
       <c r="E41">
-        <v>-23.15171222907211</v>
+        <v>-25.28695112232479</v>
       </c>
       <c r="F41">
-        <v>-1.470492281307703</v>
+        <v>-1.670546322553395</v>
       </c>
       <c r="G41">
-        <v>-5.925851181599445</v>
+        <v>-3.202454067536777</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.80733186301994</v>
       </c>
       <c r="E42">
-        <v>-22.95725049823473</v>
+        <v>-24.30269182523165</v>
       </c>
       <c r="F42">
-        <v>-1.65158664943812</v>
+        <v>-2.009891999314629</v>
       </c>
       <c r="G42">
-        <v>-4.922216264277374</v>
+        <v>-3.907358597577173</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.918872053296887</v>
       </c>
       <c r="E43">
-        <v>-22.60026183526206</v>
+        <v>-24.47256394220738</v>
       </c>
       <c r="F43">
-        <v>-1.488940023368048</v>
+        <v>-2.063922263162227</v>
       </c>
       <c r="G43">
-        <v>-5.350829284701275</v>
+        <v>-2.972288388918948</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.012843572818501</v>
       </c>
       <c r="E44">
-        <v>-22.72311933509016</v>
+        <v>-23.9706278831972</v>
       </c>
       <c r="F44">
-        <v>-1.59922471753976</v>
+        <v>-1.972251812898823</v>
       </c>
       <c r="G44">
-        <v>-5.537613574572495</v>
+        <v>-3.152272818252505</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.090685063739921</v>
       </c>
       <c r="E45">
-        <v>-22.53879232908195</v>
+        <v>-23.60446000341098</v>
       </c>
       <c r="F45">
-        <v>-1.546230741313065</v>
+        <v>-2.151516317436455</v>
       </c>
       <c r="G45">
-        <v>-5.173556192164382</v>
+        <v>-3.091676592701685</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.158829971506693</v>
       </c>
       <c r="E46">
-        <v>-21.87155791184378</v>
+        <v>-23.27509956035911</v>
       </c>
       <c r="F46">
-        <v>-1.709555800286029</v>
+        <v>-1.905641133304909</v>
       </c>
       <c r="G46">
-        <v>-4.765951893732695</v>
+        <v>-3.270505641642036</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.223139773933078</v>
       </c>
       <c r="E47">
-        <v>-21.2024260639964</v>
+        <v>-23.10846983077287</v>
       </c>
       <c r="F47">
-        <v>-1.644853679188166</v>
+        <v>-2.226891124151988</v>
       </c>
       <c r="G47">
-        <v>-5.36566383926275</v>
+        <v>-2.950117665442449</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.289259466837799</v>
       </c>
       <c r="E48">
-        <v>-21.1891440497319</v>
+        <v>-22.16256218005068</v>
       </c>
       <c r="F48">
-        <v>-2.0950721909771</v>
+        <v>-2.165068408146255</v>
       </c>
       <c r="G48">
-        <v>-5.278682565763938</v>
+        <v>-3.05177127677131</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.363811065855793</v>
       </c>
       <c r="E49">
-        <v>-21.46941130606662</v>
+        <v>-20.99719109349477</v>
       </c>
       <c r="F49">
-        <v>-1.884379427177254</v>
+        <v>-2.408674693961534</v>
       </c>
       <c r="G49">
-        <v>-5.008164647567932</v>
+        <v>-3.036582493837134</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.450042598583655</v>
       </c>
       <c r="E50">
-        <v>-20.69229346703233</v>
+        <v>-21.63775279882776</v>
       </c>
       <c r="F50">
-        <v>-2.004576365690865</v>
+        <v>-2.184438123125916</v>
       </c>
       <c r="G50">
-        <v>-4.849791459514738</v>
+        <v>-2.877603475950253</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.552298792802606</v>
       </c>
       <c r="E51">
-        <v>-20.63173418412776</v>
+        <v>-20.91565139051266</v>
       </c>
       <c r="F51">
-        <v>-2.095666130404907</v>
+        <v>-2.425777167359732</v>
       </c>
       <c r="G51">
-        <v>-5.651936643680147</v>
+        <v>-2.932161266437442</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.674411791788075</v>
       </c>
       <c r="E52">
-        <v>-19.3855117226389</v>
+        <v>-20.93733825253539</v>
       </c>
       <c r="F52">
-        <v>-1.937717175876111</v>
+        <v>-2.351313564787279</v>
       </c>
       <c r="G52">
-        <v>-5.559529386042469</v>
+        <v>-3.138692960450415</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.815225517704325</v>
       </c>
       <c r="E53">
-        <v>-19.0938055409608</v>
+        <v>-20.34634975216437</v>
       </c>
       <c r="F53">
-        <v>-2.263039420875353</v>
+        <v>-2.233669654609096</v>
       </c>
       <c r="G53">
-        <v>-4.720839089669047</v>
+        <v>-3.202924165003354</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.976696111355302</v>
       </c>
       <c r="E54">
-        <v>-18.71078268091804</v>
+        <v>-19.93925352429683</v>
       </c>
       <c r="F54">
-        <v>-2.380996453931794</v>
+        <v>-2.341216594514556</v>
       </c>
       <c r="G54">
-        <v>-4.980207090488787</v>
+        <v>-3.642412327523761</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.158674607925558</v>
       </c>
       <c r="E55">
-        <v>-18.86453343042646</v>
+        <v>-19.34239159313786</v>
       </c>
       <c r="F55">
-        <v>-2.417714667428285</v>
+        <v>-2.548057449891384</v>
       </c>
       <c r="G55">
-        <v>-5.600772162370711</v>
+        <v>-3.329622053336802</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.358199604948683</v>
       </c>
       <c r="E56">
-        <v>-17.14374953530379</v>
+        <v>-18.67412468382595</v>
       </c>
       <c r="F56">
-        <v>-2.19855350366962</v>
+        <v>-2.371904293318666</v>
       </c>
       <c r="G56">
-        <v>-5.825763458310659</v>
+        <v>-3.71686649670197</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.575922451872223</v>
       </c>
       <c r="E57">
-        <v>-17.75075524823994</v>
+        <v>-17.53468363943795</v>
       </c>
       <c r="F57">
-        <v>-2.343885594286376</v>
+        <v>-2.397501674432574</v>
       </c>
       <c r="G57">
-        <v>-5.458114133992436</v>
+        <v>-3.924013952185247</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.809698015582199</v>
       </c>
       <c r="E58">
-        <v>-17.63556898338084</v>
+        <v>-17.9182227455176</v>
       </c>
       <c r="F58">
-        <v>-2.247553920647419</v>
+        <v>-2.586608012082868</v>
       </c>
       <c r="G58">
-        <v>-6.631156287650092</v>
+        <v>-4.286144597089504</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.05747039555256</v>
       </c>
       <c r="E59">
-        <v>-17.08358422963788</v>
+        <v>-18.26789339449387</v>
       </c>
       <c r="F59">
-        <v>-2.220646890669685</v>
+        <v>-2.510007221611192</v>
       </c>
       <c r="G59">
-        <v>-5.967130373928617</v>
+        <v>-4.22833916142829</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.31662111810124</v>
       </c>
       <c r="E60">
-        <v>-16.40526863650295</v>
+        <v>-17.06439708526738</v>
       </c>
       <c r="F60">
-        <v>-2.18684204532884</v>
+        <v>-2.718519722406869</v>
       </c>
       <c r="G60">
-        <v>-5.88544597329264</v>
+        <v>-4.481516442089593</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.579778984319756</v>
       </c>
       <c r="E61">
-        <v>-17.27892448443275</v>
+        <v>-17.54922909795059</v>
       </c>
       <c r="F61">
-        <v>-2.498499541651501</v>
+        <v>-2.876617783068169</v>
       </c>
       <c r="G61">
-        <v>-6.084793783485393</v>
+        <v>-4.528036228007432</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.842439676924047</v>
       </c>
       <c r="E62">
-        <v>-16.67592647099339</v>
+        <v>-17.10837762482987</v>
       </c>
       <c r="F62">
-        <v>-2.581841586047159</v>
+        <v>-2.906453920182202</v>
       </c>
       <c r="G62">
-        <v>-6.418185582563238</v>
+        <v>-4.942552945525117</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.10069625758308</v>
       </c>
       <c r="E63">
-        <v>-15.90365862762131</v>
+        <v>-17.01791682805265</v>
       </c>
       <c r="F63">
-        <v>-2.481812908689508</v>
+        <v>-2.684497016439088</v>
       </c>
       <c r="G63">
-        <v>-7.04697736011025</v>
+        <v>-4.641369443998842</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.346998779758004</v>
       </c>
       <c r="E64">
-        <v>-15.21775331204952</v>
+        <v>-16.45200701673611</v>
       </c>
       <c r="F64">
-        <v>-2.327850886470386</v>
+        <v>-2.592181267968903</v>
       </c>
       <c r="G64">
-        <v>-7.09039847540333</v>
+        <v>-5.62085062106639</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.579470834818946</v>
       </c>
       <c r="E65">
-        <v>-15.27650120535103</v>
+        <v>-16.00671763908788</v>
       </c>
       <c r="F65">
-        <v>-2.602457993968033</v>
+        <v>-2.741072024948086</v>
       </c>
       <c r="G65">
-        <v>-7.134600879443679</v>
+        <v>-5.155162801148191</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.79447654123387</v>
       </c>
       <c r="E66">
-        <v>-15.44042290748068</v>
+        <v>-15.0086827240634</v>
       </c>
       <c r="F66">
-        <v>-2.464828063462507</v>
+        <v>-2.871406523737157</v>
       </c>
       <c r="G66">
-        <v>-7.342728256406581</v>
+        <v>-5.525053364796499</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.987471603959163</v>
       </c>
       <c r="E67">
-        <v>-15.51744772187715</v>
+        <v>-16.4202397715723</v>
       </c>
       <c r="F67">
-        <v>-2.285184995021795</v>
+        <v>-2.799620204610552</v>
       </c>
       <c r="G67">
-        <v>-7.557413824082778</v>
+        <v>-5.73377663995647</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.156853960040776</v>
       </c>
       <c r="E68">
-        <v>-14.59436358015362</v>
+        <v>-15.9040027916459</v>
       </c>
       <c r="F68">
-        <v>-2.432074416355814</v>
+        <v>-3.018112875875158</v>
       </c>
       <c r="G68">
-        <v>-8.775836935992764</v>
+        <v>-5.601169427835423</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.298647717645059</v>
       </c>
       <c r="E69">
-        <v>-14.36529977942363</v>
+        <v>-15.31278333910049</v>
       </c>
       <c r="F69">
-        <v>-2.315751752185097</v>
+        <v>-2.838027459241351</v>
       </c>
       <c r="G69">
-        <v>-7.499178017501459</v>
+        <v>-6.016258869731401</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.410516414138627</v>
       </c>
       <c r="E70">
-        <v>-15.31479398155989</v>
+        <v>-15.34897943184379</v>
       </c>
       <c r="F70">
-        <v>-2.636946242416188</v>
+        <v>-3.07892332691467</v>
       </c>
       <c r="G70">
-        <v>-7.614279064810839</v>
+        <v>-6.167699775425362</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.492920501997233</v>
       </c>
       <c r="E71">
-        <v>-14.74844490826461</v>
+        <v>-15.58988519210384</v>
       </c>
       <c r="F71">
-        <v>-2.506509026069169</v>
+        <v>-3.308922849771564</v>
       </c>
       <c r="G71">
-        <v>-8.371602772920054</v>
+        <v>-6.185030481323446</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.545150815845535</v>
       </c>
       <c r="E72">
-        <v>-15.91423261442922</v>
+        <v>-15.62867157197954</v>
       </c>
       <c r="F72">
-        <v>-2.639823162406111</v>
+        <v>-2.897881974298032</v>
       </c>
       <c r="G72">
-        <v>-7.585404486617316</v>
+        <v>-5.66623157931872</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.570382016897758</v>
       </c>
       <c r="E73">
-        <v>-14.73762638386028</v>
+        <v>-14.25925650358602</v>
       </c>
       <c r="F73">
-        <v>-2.599702843986322</v>
+        <v>-3.334030665750417</v>
       </c>
       <c r="G73">
-        <v>-8.015311930347073</v>
+        <v>-6.418963560764967</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.574455337560579</v>
       </c>
       <c r="E74">
-        <v>-15.91500245501053</v>
+        <v>-15.74831385526219</v>
       </c>
       <c r="F74">
-        <v>-2.577487686978045</v>
+        <v>-3.353485702572566</v>
       </c>
       <c r="G74">
-        <v>-8.344880049327058</v>
+        <v>-6.33509751061861</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.559047702387256</v>
       </c>
       <c r="E75">
-        <v>-15.78147587042036</v>
+        <v>-15.61067994474707</v>
       </c>
       <c r="F75">
-        <v>-2.602964954818547</v>
+        <v>-3.29386644385828</v>
       </c>
       <c r="G75">
-        <v>-8.095778050224597</v>
+        <v>-6.184543831129174</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.529348239502893</v>
       </c>
       <c r="E76">
-        <v>-15.96253331819504</v>
+        <v>-15.73260005045557</v>
       </c>
       <c r="F76">
-        <v>-3.092323826389757</v>
+        <v>-3.648758920035255</v>
       </c>
       <c r="G76">
-        <v>-7.291653159826705</v>
+        <v>-6.309424229961562</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.491663393335298</v>
       </c>
       <c r="E77">
-        <v>-16.74480003217604</v>
+        <v>-16.12068574443892</v>
       </c>
       <c r="F77">
-        <v>-2.613433862055127</v>
+        <v>-3.475169560574202</v>
       </c>
       <c r="G77">
-        <v>-7.143784332769618</v>
+        <v>-6.384335254424189</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.451577655294159</v>
       </c>
       <c r="E78">
-        <v>-16.589500544557</v>
+        <v>-16.26931478984466</v>
       </c>
       <c r="F78">
-        <v>-2.943512592681243</v>
+        <v>-3.497697840460738</v>
       </c>
       <c r="G78">
-        <v>-7.627468278239295</v>
+        <v>-6.188238399951</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.417028236033838</v>
       </c>
       <c r="E79">
-        <v>-16.75617103040931</v>
+        <v>-17.13360575352661</v>
       </c>
       <c r="F79">
-        <v>-2.95162810812647</v>
+        <v>-3.515892102095826</v>
       </c>
       <c r="G79">
-        <v>-7.995918754578021</v>
+        <v>-6.001344862076984</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.392756308515793</v>
       </c>
       <c r="E80">
-        <v>-17.31586777538732</v>
+        <v>-17.03649715690612</v>
       </c>
       <c r="F80">
-        <v>-2.876382526725774</v>
+        <v>-3.761661255199814</v>
       </c>
       <c r="G80">
-        <v>-7.916333239813942</v>
+        <v>-5.704127394106757</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.381976407936413</v>
       </c>
       <c r="E81">
-        <v>-17.90631738735143</v>
+        <v>-18.04182744355696</v>
       </c>
       <c r="F81">
-        <v>-3.146605913927806</v>
+        <v>-3.754592796151726</v>
       </c>
       <c r="G81">
-        <v>-7.507593424262286</v>
+        <v>-5.453439643690985</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.389164481836829</v>
       </c>
       <c r="E82">
-        <v>-18.56510620056529</v>
+        <v>-19.07349986351041</v>
       </c>
       <c r="F82">
-        <v>-3.331699639878939</v>
+        <v>-3.962097173818196</v>
       </c>
       <c r="G82">
-        <v>-7.504610622731402</v>
+        <v>-5.805638651977429</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.413342749437021</v>
       </c>
       <c r="E83">
-        <v>-19.69801265696022</v>
+        <v>-19.19707286223172</v>
       </c>
       <c r="F83">
-        <v>-3.581729086535525</v>
+        <v>-4.020811026961223</v>
       </c>
       <c r="G83">
-        <v>-7.617536641621482</v>
+        <v>-5.430788891111292</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.45473572620643</v>
       </c>
       <c r="E84">
-        <v>-20.84941340120247</v>
+        <v>-19.43378072708666</v>
       </c>
       <c r="F84">
-        <v>-3.330456260407337</v>
+        <v>-3.996506727363085</v>
       </c>
       <c r="G84">
-        <v>-7.740771699320852</v>
+        <v>-5.158811022332467</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.514757660014425</v>
       </c>
       <c r="E85">
-        <v>-20.60625698936061</v>
+        <v>-20.41724301275445</v>
       </c>
       <c r="F85">
-        <v>-3.494052195521017</v>
+        <v>-4.191402524791545</v>
       </c>
       <c r="G85">
-        <v>-7.684843342980404</v>
+        <v>-5.559833956232083</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.589267595656718</v>
       </c>
       <c r="E86">
-        <v>-21.66253713707174</v>
+        <v>-22.44437817449603</v>
       </c>
       <c r="F86">
-        <v>-3.500028866332215</v>
+        <v>-4.171268226699099</v>
       </c>
       <c r="G86">
-        <v>-6.86214960265274</v>
+        <v>-5.314721164504444</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.677711870018609</v>
       </c>
       <c r="E87">
-        <v>-23.4561071949197</v>
+        <v>-23.13131145366756</v>
       </c>
       <c r="F87">
-        <v>-3.699562692848949</v>
+        <v>-4.263344576989875</v>
       </c>
       <c r="G87">
-        <v>-7.747018698753457</v>
+        <v>-5.324930886947556</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.77858872183503</v>
       </c>
       <c r="E88">
-        <v>-25.09405624349407</v>
+        <v>-24.16641192844482</v>
       </c>
       <c r="F88">
-        <v>-3.677529776669288</v>
+        <v>-4.395512252841343</v>
       </c>
       <c r="G88">
-        <v>-7.296304476309381</v>
+        <v>-5.029517666296232</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.88898994002006</v>
       </c>
       <c r="E89">
-        <v>-26.81556016598396</v>
+        <v>-25.7139816927741</v>
       </c>
       <c r="F89">
-        <v>-4.14738059590457</v>
+        <v>-4.301368297513179</v>
       </c>
       <c r="G89">
-        <v>-6.88226778789489</v>
+        <v>-5.456240365217209</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.007510715483065</v>
       </c>
       <c r="E90">
-        <v>-27.75596119231282</v>
+        <v>-27.63549019828676</v>
       </c>
       <c r="F90">
-        <v>-4.168252140985507</v>
+        <v>-4.403671671758918</v>
       </c>
       <c r="G90">
-        <v>-7.351484649357953</v>
+        <v>-5.185537056471004</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.128955572400031</v>
       </c>
       <c r="E91">
-        <v>-28.636925997291</v>
+        <v>-30.16754794764658</v>
       </c>
       <c r="F91">
-        <v>-3.952575918890419</v>
+        <v>-4.601330074475714</v>
       </c>
       <c r="G91">
-        <v>-7.669253984035977</v>
+        <v>-5.83929365792966</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.248588486798656</v>
       </c>
       <c r="E92">
-        <v>-30.69046216249729</v>
+        <v>-30.96295855743485</v>
       </c>
       <c r="F92">
-        <v>-4.056685134074261</v>
+        <v>-4.392442323246567</v>
       </c>
       <c r="G92">
-        <v>-7.777409506803966</v>
+        <v>-5.690405182846478</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.364101749697491</v>
       </c>
       <c r="E93">
-        <v>-32.25966444716122</v>
+        <v>-32.95989559025627</v>
       </c>
       <c r="F93">
-        <v>-3.898712985258186</v>
+        <v>-4.700179156651778</v>
       </c>
       <c r="G93">
-        <v>-7.979524933067551</v>
+        <v>-6.211104337990746</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.468300146080875</v>
       </c>
       <c r="E94">
-        <v>-35.25982376198291</v>
+        <v>-34.93206187025574</v>
       </c>
       <c r="F94">
-        <v>-4.055281879693919</v>
+        <v>-4.474366202648633</v>
       </c>
       <c r="G94">
-        <v>-8.319044551938585</v>
+        <v>-6.074488055221642</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.560386146943918</v>
       </c>
       <c r="E95">
-        <v>-37.11887781821878</v>
+        <v>-37.38413318321808</v>
       </c>
       <c r="F95">
-        <v>-3.990579758596054</v>
+        <v>-4.36343621027014</v>
       </c>
       <c r="G95">
-        <v>-8.415434395860006</v>
+        <v>-6.87364050621955</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.640334842746951</v>
       </c>
       <c r="E96">
-        <v>-39.36096379144544</v>
+        <v>-38.82155008154778</v>
       </c>
       <c r="F96">
-        <v>-3.746204747830978</v>
+        <v>-4.329272681843883</v>
       </c>
       <c r="G96">
-        <v>-8.687031551901814</v>
+        <v>-6.444279302503773</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.706159835499522</v>
       </c>
       <c r="E97">
-        <v>-41.78184297544294</v>
+        <v>-41.64412981663268</v>
       </c>
       <c r="F97">
-        <v>-3.994331434563334</v>
+        <v>-4.093575647990534</v>
       </c>
       <c r="G97">
-        <v>-8.40910132224338</v>
+        <v>-7.007062112543257</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.755213049900201</v>
       </c>
       <c r="E98">
-        <v>-43.80155370404894</v>
+        <v>-43.82206995554069</v>
       </c>
       <c r="F98">
-        <v>-3.749943998287215</v>
+        <v>-4.324774646846682</v>
       </c>
       <c r="G98">
-        <v>-8.385715628553967</v>
+        <v>-6.673120762905894</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.786105862947641</v>
       </c>
       <c r="E99">
-        <v>-46.66537878039571</v>
+        <v>-45.74797560931481</v>
       </c>
       <c r="F99">
-        <v>-3.890482326743971</v>
+        <v>-4.001658344241095</v>
       </c>
       <c r="G99">
-        <v>-9.219843993174276</v>
+        <v>-7.145323736445379</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-9.791179053549822</v>
       </c>
       <c r="E100">
-        <v>-49.16355222299313</v>
+        <v>-49.06886862420375</v>
       </c>
       <c r="F100">
-        <v>-3.662312667479861</v>
+        <v>-4.106607523971376</v>
       </c>
       <c r="G100">
-        <v>-9.371268346140539</v>
+        <v>-7.344426566268226</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-9.774299410580038</v>
       </c>
       <c r="E101">
-        <v>-51.56423780927192</v>
+        <v>-50.77240582606822</v>
       </c>
       <c r="F101">
-        <v>-3.644097696659702</v>
+        <v>-3.82076278428735</v>
       </c>
       <c r="G101">
-        <v>-9.568186215907469</v>
+        <v>-7.883254268785544</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.722257106433588</v>
       </c>
       <c r="E102">
-        <v>-53.19554245435854</v>
+        <v>-53.03291363155807</v>
       </c>
       <c r="F102">
-        <v>-3.735172550760494</v>
+        <v>-3.84245772656667</v>
       </c>
       <c r="G102">
-        <v>-9.647496955391789</v>
+        <v>-7.898390082991092</v>
       </c>
     </row>
   </sheetData>
